--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Arquitectura_Fisica.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Arquitectura_Fisica.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(a) Modelo de Emplazamiento Híb" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(b) Tecnologías de Software a U" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c.1 Infraestructura de cómputo " sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c.2 Red y seguridad" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c.3 Dispositivos de terreno y o" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c.4 Resumen del inventario ofer" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(d) Especificaciones Data Cente" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(e) Especificaciones Data Cente" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operación Desconectada (RT-03.1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="(a) Modelo de Emplazamiento Híb" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="(b) Tecnologías de Software a U" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="c.1 Infraestructura de cómputo " sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="c.2 Red y seguridad" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="c.3 Dispositivos de terreno y o" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="c.4 Resumen del inventario ofer" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="(d) Especificaciones Data Cente" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="(e) Especificaciones Data Cente" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Operación Desconectada (RT-03.1" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Django monolito modular (Python) + Celery sobre AWS ECS Fargate (2–6 tareas con escala automática). La misma imagen se reutiliza en modo wms_only dentro del ambiente on-premise (RT-02.02).</t>
+          <t>Monolito modular Laravel 13 sobre PHP 8.5 (dependencias fijadas por composer.lock) en AWS ECS Fargate, con perfiles separados de API (PHP-FPM, 2–4 tareas y techo de 8), consumo de reconciliación, trabajos y planificador. La misma imagen se ejecuta en el perfil wms_only dentro del ambiente on-premise (RT-02.02).</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Keycloak en ECS/Fargate (OIDC/OAuth 2.1, MFA, SSO), autoridad única de identidad en sa-east-1 (RT-12.01); las cachés locales on-premise (A-05, VM-05/VM-C03) son de solo lectura con TTL de 8 h, sin autoridades de identidad dispersas (Modelo B, D6).</t>
+          <t>Keycloak en ECS/Fargate (OIDC/OAuth 2.1, MFA, SSO), autoridad única de identidad en sa-east-1 (RT-12.01); las cachés locales on-premise (A-05, VM-05/VM-C03/E-01) son de solo lectura de 24 h, no emiten sesiones y el verificador local habilita los relevos sin enlace; el backend Laravel valida los JWT OIDC sin un segundo emisor.</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Toma de pedido, entrega, POD, devoluciones y cobros contra caché local y buffer idempotente (RNF-06.02, RT-03.10); sesión sostenida por caché de identidad A-05 (TTL 8 h para bodega, 14 h para reparto/preventa).</t>
+          <t>Toma de pedido, entrega, POD, devoluciones y cobros contra caché local y buffer idempotente (RNF-06.02, RT-03.10); sesión sostenida por la credencial de turno (hasta 8 h en bodega y 14 h en reparto y preventa); en bodega, la caché de identidad A-05 (24 h) y el verificador local habilitan los relevos sin enlace.</t>
         </is>
       </c>
     </row>
